--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>323</v>
+        <v>410</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>302</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>302</v>
+        <v>355</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>282</v>
+        <v>322</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>282</v>
+        <v>322</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>405</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,10 +463,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>443</v>
+        <v>410</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -495,10 +495,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -508,17 +508,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,10 +527,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -540,17 +540,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,10 +559,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -572,17 +572,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,10 +623,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -636,17 +636,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -668,17 +668,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,10 +719,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -732,17 +732,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>552</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>542</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>376</v>
+        <v>498</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>376</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -568,21 +568,21 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>376</v>
+        <v>457</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Panaf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Panaff</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>356</v>
+        <v>440</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -696,21 +696,21 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,25 +719,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>323</v>
+        <v>407</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>322</v>
+        <v>406</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>497</v>
+        <v>541</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>457</v>
+        <v>501</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>496</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>407</v>
+        <v>485</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -760,21 +760,21 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>611</v>
+        <v>903</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>601</v>
+        <v>859</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>557</v>
+        <v>741</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
@@ -536,16 +536,16 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>556</v>
+        <v>726</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>516</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Panaf</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Panaff</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>693</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>503</v>
+        <v>691</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>500</v>
+        <v>683</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>498</v>
+        <v>668</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>466</v>
+        <v>665</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>903</v>
+        <v>1025</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>859</v>
+        <v>903</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>741</v>
+        <v>859</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>726</v>
+        <v>746</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>693</v>
+        <v>733</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
@@ -632,21 +632,21 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>691</v>
+        <v>726</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
@@ -664,21 +664,21 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
@@ -728,21 +728,21 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1025</v>
+        <v>1154</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>903</v>
+        <v>1025</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>859</v>
+        <v>1019</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>746</v>
+        <v>1007</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>1004</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>733</v>
+        <v>915</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>726</v>
+        <v>892</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>710</v>
+        <v>876</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>691</v>
+        <v>839</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>683</v>
+        <v>833</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -472,7 +472,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1025</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1019</v>
+        <v>1065</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,25 +559,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1007</v>
+        <v>1025</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>892</v>
+        <v>922</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>876</v>
+        <v>915</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>839</v>
+        <v>879</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>833</v>
+        <v>859</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,25 +463,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1154</v>
+        <v>1427</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -495,25 +495,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1080</v>
+        <v>1358</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1065</v>
+        <v>1347</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1025</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1007</v>
+        <v>1220</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>938</v>
+        <v>1201</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>922</v>
+        <v>1190</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>915</v>
+        <v>1166</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>879</v>
+        <v>1148</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>859</v>
+        <v>1125</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1427</v>
+        <v>1458</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,25 +495,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1358</v>
+        <v>1441</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1347</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1356</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1220</v>
+        <v>1335</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1201</v>
+        <v>1333</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1190</v>
+        <v>1331</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1166</v>
+        <v>1249</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -719,25 +719,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1148</v>
+        <v>1244</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -751,25 +751,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1125</v>
+        <v>1242</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1458</v>
+        <v>1682</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1441</v>
+        <v>1667</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1427</v>
+        <v>1641</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1356</v>
+        <v>1574</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1335</v>
+        <v>1533</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1333</v>
+        <v>1525</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1331</v>
+        <v>1521</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1249</v>
+        <v>1518</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1244</v>
+        <v>1509</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1242</v>
+        <v>1485</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1682</v>
+        <v>1863</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1667</v>
+        <v>1853</v>
       </c>
       <c r="C3" t="n">
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1641</v>
+        <v>1840</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1574</v>
+        <v>1758</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1533</v>
+        <v>1751</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1525</v>
+        <v>1732</v>
       </c>
       <c r="C7" t="n">
         <v>20</v>
@@ -632,21 +632,21 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1521</v>
+        <v>1717</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1518</v>
+        <v>1708</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1509</v>
+        <v>1705</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1485</v>
+        <v>1671</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1863</v>
+        <v>2010</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -495,25 +495,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1853</v>
+        <v>2007</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1840</v>
+        <v>1980</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1758</v>
+        <v>1953</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1751</v>
+        <v>1896</v>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1732</v>
+        <v>1884</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1717</v>
+        <v>1844</v>
       </c>
       <c r="C8" t="n">
         <v>22</v>
@@ -664,21 +664,21 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1708</v>
+        <v>1841</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,25 +719,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1705</v>
+        <v>1837</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1671</v>
+        <v>1814</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2010</v>
+        <v>2209</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2007</v>
+        <v>2162</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1980</v>
+        <v>2155</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1953</v>
+        <v>2125</v>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1896</v>
+        <v>2078</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1884</v>
+        <v>2066</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,25 +655,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1844</v>
+        <v>2041</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1841</v>
+        <v>2026</v>
       </c>
       <c r="C9" t="n">
         <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1837</v>
+        <v>2010</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1814</v>
+        <v>2007</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2209</v>
+        <v>2292</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2162</v>
+        <v>2275</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2155</v>
+        <v>2269</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2125</v>
+        <v>2265</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2078</v>
+        <v>2228</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2066</v>
+        <v>2185</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2041</v>
+        <v>2179</v>
       </c>
       <c r="C8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2026</v>
+        <v>2163</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2010</v>
+        <v>2147</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2007</v>
+        <v>2144</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2292</v>
+        <v>2635</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2275</v>
+        <v>2618</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2269</v>
+        <v>2551</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2265</v>
+        <v>2524</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2228</v>
+        <v>2499</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2185</v>
+        <v>2472</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2179</v>
+        <v>2431</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2163</v>
+        <v>2431</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2147</v>
+        <v>2402</v>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2144</v>
+        <v>2364</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2635</v>
+        <v>2940</v>
       </c>
       <c r="C2" t="n">
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2618</v>
+        <v>2892</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2524</v>
+        <v>2772</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2499</v>
+        <v>2761</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2472</v>
+        <v>2664</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2431</v>
+        <v>2608</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>catherine</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>catherine#5FRTD</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2431</v>
+        <v>2588</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2402</v>
+        <v>2581</v>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2364</v>
+        <v>2581</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2940</v>
+        <v>3242</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2892</v>
+        <v>3209</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,25 +527,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>3106</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2772</v>
+        <v>3103</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2761</v>
+        <v>3029</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2664</v>
+        <v>3000</v>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,25 +655,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2608</v>
+        <v>2914</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>catherine</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>catherine#5FRTD</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2588</v>
+        <v>2902</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2581</v>
+        <v>2875</v>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2581</v>
+        <v>2864</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3242</v>
+        <v>3624</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3209</v>
+        <v>3413</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3106</v>
+        <v>3357</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3103</v>
+        <v>3317</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3029</v>
+        <v>3290</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3000</v>
+        <v>3263</v>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2914</v>
+        <v>3234</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2902</v>
+        <v>3225</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2875</v>
+        <v>3215</v>
       </c>
       <c r="C10" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2864</v>
+        <v>3201</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -472,7 +472,7 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3413</v>
+        <v>3477</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3357</v>
+        <v>3431</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3317</v>
+        <v>3421</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3290</v>
+        <v>3354</v>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3263</v>
+        <v>3327</v>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3234</v>
+        <v>3298</v>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3225</v>
+        <v>3266</v>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3215</v>
+        <v>3265</v>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3201</v>
+        <v>3235</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3624</v>
+        <v>3676</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3477</v>
+        <v>3624</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3431</v>
+        <v>3553</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3421</v>
+        <v>3496</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3354</v>
+        <v>3486</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3327</v>
+        <v>3470</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3298</v>
+        <v>3454</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3266</v>
+        <v>3441</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3265</v>
+        <v>3434</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3235</v>
+        <v>3392</v>
       </c>
       <c r="C11" t="n">
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3676</v>
+        <v>3828</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3624</v>
+        <v>3770</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3553</v>
+        <v>3746</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3496</v>
+        <v>3733</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3486</v>
+        <v>3693</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3470</v>
+        <v>3630</v>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3454</v>
+        <v>3576</v>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3441</v>
+        <v>3567</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3434</v>
+        <v>3550</v>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3392</v>
+        <v>3544</v>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3828</v>
+        <v>3867</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3770</v>
+        <v>3809</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3746</v>
+        <v>3772</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3733</v>
+        <v>3746</v>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3693</v>
+        <v>3732</v>
       </c>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3630</v>
+        <v>3669</v>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3576</v>
+        <v>3615</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3567</v>
+        <v>3606</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3550</v>
+        <v>3598</v>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3544</v>
+        <v>3589</v>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,25 +463,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3867</v>
+        <v>3941</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>3904</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3772</v>
+        <v>3878</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3746</v>
+        <v>3867</v>
       </c>
       <c r="C5" t="n">
         <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3732</v>
+        <v>3784</v>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3669</v>
+        <v>3730</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3615</v>
+        <v>3721</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3606</v>
+        <v>3721</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3598</v>
+        <v>3718</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3589</v>
+        <v>3678</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3941</v>
+        <v>4136</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3904</v>
+        <v>4099</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3878</v>
+        <v>4053</v>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3867</v>
+        <v>3959</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3784</v>
+        <v>3923</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3730</v>
+        <v>3916</v>
       </c>
       <c r="C7" t="n">
         <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3721</v>
+        <v>3913</v>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3721</v>
+        <v>3908</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3718</v>
+        <v>3896</v>
       </c>
       <c r="C10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3678</v>
+        <v>3844</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4136</v>
+        <v>4353</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4099</v>
+        <v>4190</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4053</v>
+        <v>4119</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3959</v>
+        <v>4110</v>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>3923</v>
+        <v>4100</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3916</v>
+        <v>4061</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3913</v>
+        <v>4057</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3908</v>
+        <v>4018</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3896</v>
+        <v>4014</v>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3844</v>
+        <v>3999</v>
       </c>
       <c r="C11" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4353</v>
+        <v>4449</v>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4190</v>
+        <v>4286</v>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4119</v>
+        <v>4285</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4110</v>
+        <v>4206</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4100</v>
+        <v>4196</v>
       </c>
       <c r="C6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4061</v>
+        <v>4157</v>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4057</v>
+        <v>4153</v>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4018</v>
+        <v>4114</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4014</v>
+        <v>4110</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3999</v>
+        <v>4095</v>
       </c>
       <c r="C11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4449</v>
+        <v>4542</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4286</v>
+        <v>4379</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4285</v>
+        <v>4289</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4206</v>
+        <v>4285</v>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -591,25 +591,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4196</v>
+        <v>4250</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>90</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -623,25 +623,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4157</v>
+        <v>4246</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4153</v>
+        <v>4206</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4114</v>
+        <v>4203</v>
       </c>
       <c r="C9" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4110</v>
+        <v>4176</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4095</v>
+        <v>4114</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4542</v>
+        <v>4642</v>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4379</v>
+        <v>4551</v>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4289</v>
+        <v>4411</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4285</v>
+        <v>4357</v>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4250</v>
+        <v>4350</v>
       </c>
       <c r="C6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4246</v>
+        <v>4318</v>
       </c>
       <c r="C7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,25 +655,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4206</v>
+        <v>4303</v>
       </c>
       <c r="C8" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -687,25 +687,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4203</v>
+        <v>4278</v>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4176</v>
+        <v>4248</v>
       </c>
       <c r="C10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,25 +751,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4114</v>
+        <v>4237</v>
       </c>
       <c r="C11" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4642</v>
+        <v>4685</v>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4551</v>
+        <v>4594</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4411</v>
+        <v>4454</v>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4357</v>
+        <v>4400</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4350</v>
+        <v>4393</v>
       </c>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4318</v>
+        <v>4361</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4303</v>
+        <v>4346</v>
       </c>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4278</v>
+        <v>4321</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4248</v>
+        <v>4291</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
         <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4237</v>
+        <v>4280</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4685</v>
+        <v>4739</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4594</v>
+        <v>4648</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4454</v>
+        <v>4508</v>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4400</v>
+        <v>4454</v>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4393</v>
+        <v>4447</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4361</v>
+        <v>4415</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4346</v>
+        <v>4400</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4321</v>
+        <v>4395</v>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4291</v>
+        <v>4375</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4280</v>
+        <v>4334</v>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4739</v>
+        <v>4819</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4648</v>
+        <v>4728</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4508</v>
+        <v>4568</v>
       </c>
       <c r="C4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4454</v>
+        <v>4534</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4447</v>
+        <v>4480</v>
       </c>
       <c r="C6" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4415</v>
+        <v>4475</v>
       </c>
       <c r="C7" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4400</v>
+        <v>4475</v>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4395</v>
+        <v>4455</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4375</v>
+        <v>4447</v>
       </c>
       <c r="C10" t="n">
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4334</v>
+        <v>4394</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4819</v>
+        <v>4980</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4728</v>
+        <v>4889</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,16 +527,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4568</v>
+        <v>4709</v>
       </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -559,16 +559,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4534</v>
+        <v>4675</v>
       </c>
       <c r="C5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4480</v>
+        <v>4636</v>
       </c>
       <c r="C6" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4475</v>
+        <v>4621</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4475</v>
+        <v>4616</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4455</v>
+        <v>4596</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4447</v>
+        <v>4588</v>
       </c>
       <c r="C10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4394</v>
+        <v>4555</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,30 +463,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4980</v>
+        <v>5004</v>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SabC1</t>
+          <t>MagicMath</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4889</v>
+        <v>4980</v>
       </c>
       <c r="C3" t="n">
         <v>72</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MagicMath</t>
+          <t>SabC1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -472,7 +472,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4709</v>
+        <v>4804</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4675</v>
+        <v>4709</v>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4636</v>
+        <v>4684</v>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -623,30 +623,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4621</v>
+        <v>4636</v>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4616</v>
+        <v>4621</v>
       </c>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4596</v>
+        <v>4616</v>
       </c>
       <c r="C9" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -719,30 +719,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4588</v>
+        <v>4596</v>
       </c>
       <c r="C10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t>David</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Daviddesco1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -751,30 +751,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4555</v>
+        <v>4588</v>
       </c>
       <c r="C11" t="n">
         <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
     </row>

--- a/mvp.xlsx
+++ b/mvp.xlsx
@@ -463,16 +463,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5004</v>
+        <v>5094</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4980</v>
+        <v>5060</v>
       </c>
       <c r="C3" t="n">
         <v>72</v>
@@ -504,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,30 +527,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>4804</v>
+        <v>4929</v>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mamadou</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mamad_Shelter</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -559,30 +559,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4709</v>
+        <v>4904</v>
       </c>
       <c r="C5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
     </row>
@@ -591,30 +591,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4684</v>
+        <v>4894</v>
       </c>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Mamadou</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Mamad_Shelter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
     </row>
@@ -623,16 +623,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>4636</v>
+        <v>4806</v>
       </c>
       <c r="C7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -655,30 +655,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>4621</v>
+        <v>4756</v>
       </c>
       <c r="C8" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>Leo_durable</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
     </row>
@@ -687,30 +687,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>4616</v>
+        <v>4711</v>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leo_durable</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
     </row>
@@ -719,16 +719,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>4596</v>
+        <v>4686</v>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -751,16 +751,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>4588</v>
+        <v>4678</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
